--- a/week3/manual_gold/301563_云汉芯城_gold.xlsx
+++ b/week3/manual_gold/301563_云汉芯城_gold.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,16 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>数据来源类型</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -496,6 +506,11 @@
           <t>2008年设立，注册资本50万元，深圳云汉电子出资50%，刘云锋出资50%</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,6 +547,11 @@
           <t>刘云锋出资50%</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -572,6 +592,11 @@
           <t>2015年12月整体变更为股份公司，以经审计净资产折股4000万股</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -608,6 +633,11 @@
           <t>2020年5月，火炬电子以现金5000万元认购新增股份113.0488万股，每股价格约44.23元</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -644,6 +674,11 @@
           <t>2020年9月，厦门西堤以5000万元认购新增股份96.899万股；中小企业基金以2000万元认购新增股份38.7596万股，每股价格约51.6元</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -678,6 +713,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>中小企业基金以2000万元认购新增股份38.7596万股</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>直接披露</t>
         </is>
       </c>
     </row>
@@ -692,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,6 +786,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>时点说明</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -790,6 +835,11 @@
           <t>2008年设立，深圳云汉电子出资50%</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -834,6 +884,11 @@
           <t>刘云锋出资50%</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -884,6 +939,11 @@
           <t>2015年12月整体变更为股份公司，折股4000万股</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -932,6 +992,11 @@
           <t>2020年5月增资后曾烨持股36.01%</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -978,6 +1043,11 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>2020年9月增资及股权转让后曾烨持股33.03%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1169,6 +1239,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>转让类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1211,6 +1286,11 @@
           <t>2018年4月第一次股权转让，丰利财富将所持股份转让给天健创投</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1253,6 +1333,11 @@
           <t>2018年6-7月增资+第二次股权转让</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>增资附带转让</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1289,6 +1374,11 @@
           <t>2019年8月，为赛咨询与李文发签署股份转让协议，李文发以40万元受让40万股</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1325,6 +1415,11 @@
           <t>秦国君以40万元受让40万股</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1361,6 +1456,11 @@
           <t>2020年9月第四次股权转让，曾烨向鸿迪投资转让48万股，每股51.6元</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1397,6 +1497,11 @@
           <t>曾烨向郦韩英转让48.4495万股</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1433,6 +1538,11 @@
           <t>刘云锋向福建开京转让11.628万股</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1473,6 +1583,11 @@
           <t>刘云锋向沈笑彦、衣嘉平、余满芬、崔振南、湘裕君源等转让股份</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1509,6 +1624,11 @@
           <t>李文发向湘裕君源转让5万股</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1543,6 +1663,11 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>秦国君向湘裕君源转让15万股</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
         </is>
       </c>
     </row>
